--- a/03_bloques/B05/B05_trabajo.xlsx
+++ b/03_bloques/B05/B05_trabajo.xlsx
@@ -587,7 +587,7 @@
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -634,7 +634,7 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -877,7 +877,7 @@
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -924,7 +924,7 @@
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
       <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       <c r="G15" s="5" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1312,7 +1312,7 @@
       <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1359,7 +1359,7 @@
       <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1453,7 +1453,7 @@
       <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1598,7 +1598,7 @@
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -1696,7 +1696,7 @@
       <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       <c r="G26" s="3" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -1986,7 +1986,7 @@
       <c r="G31" s="3" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2033,7 +2033,7 @@
       <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
       <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2178,7 +2178,7 @@
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2225,7 +2225,7 @@
       <c r="G36" s="3" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       <c r="G38" s="3" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2511,7 +2511,7 @@
       <c r="G42" s="3" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
       <c r="G45" s="3" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2750,7 +2750,7 @@
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2797,7 +2797,7 @@
       <c r="G48" s="3" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2895,7 +2895,7 @@
       <c r="G50" s="3" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       <c r="G51" s="3" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       <c r="G52" s="3" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       <c r="G54" s="3" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3134,7 +3134,7 @@
       <c r="G55" s="3" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
       <c r="G56" s="3" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -3373,7 +3373,7 @@
       <c r="G60" s="3" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       <c r="G61" s="3" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -3467,7 +3467,7 @@
       <c r="G62" s="3" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3659,7 +3659,7 @@
       <c r="G66" s="3" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       <c r="G67" s="3" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3753,7 +3753,7 @@
       <c r="G68" s="3" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3851,7 +3851,7 @@
       <c r="G70" s="3" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3945,7 +3945,7 @@
       <c r="G72" s="5" t="inlineStr"/>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -3992,7 +3992,7 @@
       <c r="G73" s="3" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       <c r="G74" s="3" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       <c r="G76" s="3" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       <c r="G78" s="5" t="inlineStr"/>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -4282,7 +4282,7 @@
       <c r="G79" s="3" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -4329,7 +4329,7 @@
       <c r="G80" s="3" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4427,7 +4427,7 @@
       <c r="G82" s="3" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       <c r="G84" s="5" t="inlineStr"/>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -4572,7 +4572,7 @@
       <c r="G85" s="5" t="inlineStr"/>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -4619,7 +4619,7 @@
       <c r="G86" s="3" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
       <c r="G87" s="3" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -4764,7 +4764,7 @@
       <c r="G89" s="3" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -4862,7 +4862,7 @@
       <c r="G91" s="5" t="inlineStr"/>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
@@ -4909,7 +4909,7 @@
       <c r="G92" s="3" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -4956,7 +4956,7 @@
       <c r="G93" s="3" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -5054,7 +5054,7 @@
       <c r="G95" s="3" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       <c r="G97" s="5" t="inlineStr"/>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
@@ -5199,7 +5199,7 @@
       <c r="G98" s="3" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       <c r="G99" s="3" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       <c r="G101" s="3" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -5391,7 +5391,7 @@
       <c r="G102" s="3" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
       <c r="G103" s="3" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       <c r="G105" s="3" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -5630,7 +5630,7 @@
       <c r="G107" s="5" t="inlineStr"/>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
@@ -5677,7 +5677,7 @@
       <c r="G108" s="3" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -5724,7 +5724,7 @@
       <c r="G109" s="3" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -5869,7 +5869,7 @@
       <c r="G112" s="5" t="inlineStr"/>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
@@ -5916,7 +5916,7 @@
       <c r="G113" s="3" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -5963,7 +5963,7 @@
       <c r="G114" s="3" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -6010,7 +6010,7 @@
       <c r="G115" s="3" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -6104,7 +6104,7 @@
       <c r="G117" s="5" t="inlineStr"/>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
@@ -6202,7 +6202,7 @@
       <c r="G119" s="3" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -6249,7 +6249,7 @@
       <c r="G120" s="3" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -6343,7 +6343,7 @@
       <c r="G122" s="5" t="inlineStr"/>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I122" s="4" t="inlineStr">
@@ -6390,7 +6390,7 @@
       <c r="G123" s="3" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       <c r="G125" s="3" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
@@ -6586,7 +6586,7 @@
       <c r="G127" s="3" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
@@ -6633,7 +6633,7 @@
       <c r="G128" s="3" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
@@ -6680,7 +6680,7 @@
       <c r="G129" s="3" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I130" s="4" t="inlineStr">
@@ -6829,7 +6829,7 @@
       <c r="G132" s="3" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
@@ -6876,7 +6876,7 @@
       <c r="G133" s="3" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -6974,7 +6974,7 @@
       <c r="G135" s="3" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
@@ -7072,7 +7072,7 @@
       <c r="G137" s="3" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
@@ -7170,7 +7170,7 @@
       <c r="G139" s="3" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
@@ -7217,7 +7217,7 @@
       <c r="G140" s="3" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       <c r="G143" s="5" t="inlineStr"/>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
@@ -7413,7 +7413,7 @@
       <c r="G144" s="3" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       <c r="G145" s="3" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       <c r="G146" s="3" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       <c r="G148" s="5" t="inlineStr"/>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
@@ -7703,7 +7703,7 @@
       <c r="G150" s="3" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
@@ -7750,7 +7750,7 @@
       <c r="G151" s="3" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       <c r="G152" s="3" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
@@ -7895,7 +7895,7 @@
       <c r="G154" s="3" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
@@ -7942,7 +7942,7 @@
       <c r="G155" s="3" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
@@ -8040,7 +8040,7 @@
       <c r="G157" s="5" t="inlineStr"/>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
@@ -8087,7 +8087,7 @@
       <c r="G158" s="3" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       <c r="G160" s="3" t="inlineStr"/>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
@@ -8232,7 +8232,7 @@
       <c r="G161" s="3" t="inlineStr"/>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       <c r="G163" s="5" t="inlineStr"/>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
@@ -8428,7 +8428,7 @@
       <c r="G165" s="3" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
@@ -8475,7 +8475,7 @@
       <c r="G166" s="3" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
@@ -8522,7 +8522,7 @@
       <c r="G167" s="3" t="inlineStr"/>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
@@ -8620,7 +8620,7 @@
       <c r="G169" s="5" t="inlineStr"/>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
@@ -8718,7 +8718,7 @@
       <c r="G171" s="3" t="inlineStr"/>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
@@ -8765,7 +8765,7 @@
       <c r="G172" s="3" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
@@ -8812,7 +8812,7 @@
       <c r="G173" s="3" t="inlineStr"/>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
@@ -8910,7 +8910,7 @@
       <c r="G175" s="5" t="inlineStr"/>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
@@ -9008,7 +9008,7 @@
       <c r="G177" s="3" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
@@ -9055,7 +9055,7 @@
       <c r="G178" s="3" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
@@ -9204,7 +9204,7 @@
       <c r="G181" s="5" t="inlineStr"/>
       <c r="H181" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
@@ -9251,7 +9251,7 @@
       <c r="G182" s="3" t="inlineStr"/>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
@@ -9298,7 +9298,7 @@
       <c r="G183" s="3" t="inlineStr"/>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
@@ -9345,7 +9345,7 @@
       <c r="G184" s="3" t="inlineStr"/>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
@@ -9494,7 +9494,7 @@
       <c r="G187" s="5" t="inlineStr"/>
       <c r="H187" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I187" s="4" t="inlineStr">
@@ -9541,7 +9541,7 @@
       <c r="G188" s="3" t="inlineStr"/>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
@@ -9588,7 +9588,7 @@
       <c r="G189" s="3" t="inlineStr"/>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
@@ -9686,7 +9686,7 @@
       <c r="G191" s="3" t="inlineStr"/>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
@@ -9733,7 +9733,7 @@
       <c r="G192" s="5" t="inlineStr"/>
       <c r="H192" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I192" s="4" t="inlineStr">
@@ -9780,7 +9780,7 @@
       <c r="G193" s="3" t="inlineStr"/>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
@@ -9827,7 +9827,7 @@
       <c r="G194" s="3" t="inlineStr"/>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
@@ -9925,7 +9925,7 @@
       <c r="G196" s="3" t="inlineStr"/>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -9972,7 +9972,7 @@
       <c r="G197" s="5" t="inlineStr"/>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I197" s="4" t="inlineStr">
@@ -10019,7 +10019,7 @@
       <c r="G198" s="3" t="inlineStr"/>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
@@ -10066,7 +10066,7 @@
       <c r="G199" s="3" t="inlineStr"/>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
@@ -10164,7 +10164,7 @@
       <c r="G201" s="3" t="inlineStr"/>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
@@ -10183,7 +10183,7 @@
   <autoFilter ref="A1:K201"/>
   <dataValidations count="1">
     <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Borrador,Sin borrador,Revisar_Juan,Enviado,Validado,Grabado"</formula1>
+      <formula1>"Borrador,Sin borrador,Por_revisar,Enviado,Validado,Grabado"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -10287,7 +10287,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Español redactado o adaptado por Claude (Revisar_Juan)</t>
+          <t>Español redactado o adaptado por Claude (Por_revisar)</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
